--- a/territory/F27-Feedback-Form-Rows.xlsx
+++ b/territory/F27-Feedback-Form-Rows.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rows for Team Tab" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rows for Ary Tsotras tab" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -476,8 +476,8 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="104" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="108" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -556,14 +556,10 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1) Account is held to Feb 1, 2027 as an FAC holdover. 2) The opportunity on it is dead, with no live communication. 3) A Feb 1 holdover is retained only by moving the opportunity to QO before that date, and a dead cycle has no path there. 4) Named contact Joseph Sacri is known to the future owner from Joseph's previous organisation, so there is an existing relationship available to restart it now. Business impact: five months of a restartable relationship going cold before the account changes hands.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) The opportunity on it is dead, with no live communication. 3) A Feb 1 holdover is retained only by moving the opportunity to QO before that date, and a dead cycle has no path there. 4) Named contact Joseph Sacri is known to me from his previous organisation, so there is an existing relationship available to restart it now. Business impact: five months of a restartable relationship going cold before the account changes hands.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,14 +594,10 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account, so there is nothing to move to QO before Feb 1. 3) Open Opportunities Proposal+ reads 0 in the territory export. 4) Same APEX group as MaxLinear, which is also held and whose opportunity is closed lost, so the group is being held as a unit with nothing live in it. Business impact: the holdover cannot achieve its purpose and delays coverage by five months.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account, so there is nothing to move to QO before Feb 1. 3) Open Opportunities Proposal+ reads 0 in the territory export. 4) Same APEX group as MaxLinear, which is also held and whose opportunity is closed lost, so the group is held as a unit with nothing live in it. Business impact: the holdover cannot achieve its purpose and delays coverage by five months.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -640,14 +632,10 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>1) Held to Feb 1, 2027 as an FAC holdover. 2) The opportunity is closed lost, with no communication on the account. 3) A closed lost opportunity cannot reach QO by Feb 1, so the holdover condition cannot be satisfied. 4) Same APEX group as Exar Corporation, which has no opportunity at all. Business impact: an entire APEX group held for five months with no live cycle in it.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) The opportunity is closed lost, with no communication on the account. 3) A closed lost opportunity cannot reach QO by Feb 1, so the holdover condition cannot be satisfied. 4) Same APEX group as Exar Corporation, which has no opportunity at all. Business impact: an entire APEX group held for five months with no live cycle in it.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -677,34 +665,30 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Holdover not reflected/owner change required?</t>
+          <t>Holdover not reflected</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>1) Held to Feb 1, 2027 as an FAC holdover. 2) The opportunity has died. 3) Black Rock City LLC (001f300001v97AfAAI) is the same organisation in the same APEX group, also held to Feb 1 under the same owner, and is a duplicate record. 4) Requesting both records release together and that Black Rock City LLC merge into this one. Business impact: two records for one organisation both frozen until February on a dead cycle.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) The opportunity has died. 3) Black Rock City LLC (001f300001v97AfAAI) is the same organisation in the same APEX group, also held to Feb 1 under the same owner, and is a duplicate record. 4) Asking that both records release together and that Black Rock City LLC merge into this one. Business impact: two records for one organisation both frozen until February on a dead cycle.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Samba Tv, Inc.</t>
+          <t>Black Rock City LLC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001v8JfRAAU/view</t>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001v97AfAAI/view</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Josh Scott</t>
+          <t>Andrew Bell</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -724,29 +708,25 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account, so nothing can reach QO before the date. 3) ITRG status is Winback, meaning a lapsed membership sits on the account. 4) Winback accounts are the highest-intent segment of the incoming book and are time-sensitive. Business impact: the single strongest re-entry point in the arriving territory sits idle until February.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover with no opportunity on the record. 2) Same organisation as Burning Man Project (001a700000LEgFFAA1), same APEX group, same current owner. 3) Black Rock City LLC is the operating entity behind the event and Burning Man Project is the nonprofit. 4) Asking for release alongside Burning Man Project and a merge into that record. Business impact: a duplicate record independently frozen until February.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Irhythm Technologies, Inc.</t>
+          <t>Samba Tv, Inc.</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/00140000011lkU3AAI/view</t>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001v8JfRAAU/view</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Cameron McLean</t>
+          <t>Josh Scott</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -766,29 +746,25 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account. 3) Open Opportunities Proposal+ reads 0 in the territory export. 4) With nothing to advance to QO, the holdover has no condition it can satisfy. Business impact: five months of lost coverage on a viable California account with no offsetting continuity benefit.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account, so nothing can reach QO before the date. 3) ITRG status is Winback, so a lapsed membership sits on the account. 4) Winbacks are the highest-intent accounts in the arriving book and are time-sensitive. Business impact: the strongest re-entry point in the territory sits idle until February.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Mode</t>
+          <t>Irhythm Technologies, Inc.</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/0013300001lNQtMAAW/view</t>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/00140000011lkU3AAI/view</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Akshat Singh</t>
+          <t>Cameron McLean</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -803,34 +779,30 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Holdover not reflected/owner change required?</t>
+          <t>Holdover not reflected</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account. 3) Separately, the APEX group is ThoughtSpot, which acquired Mode Analytics. If that group carries larges, the account may belong in LE rather than SMB. 4) Raising both together so the group question is settled before the account is worked. Business impact: either five months of dead hold, or an account worked in the wrong segment.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account. 3) Open Opportunities Proposal+ reads 0 in the territory export. 4) With nothing to advance to QO, the holdover has no condition it can satisfy. Business impact: five months of lost coverage on a viable California account with no offsetting continuity benefit.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Black Rock City LLC</t>
+          <t>Mode</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001v97AfAAI/view</t>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/0013300001lNQtMAAW/view</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Andrew Bell</t>
+          <t>Akshat Singh</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -845,19 +817,15 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Holdover not reflected/owner change required?</t>
+          <t>Holdover not reflected</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>1) Held to Feb 1, 2027 as an FAC holdover with no opportunity on the record. 2) This is the same organisation as Burning Man Project (001a700000LEgFFAA1), in the same APEX group and under the same current owner. 3) Black Rock City LLC is the operating entity behind the event; Burning Man Project is the nonprofit. 4) Requesting release with Burning Man Project and a merge into that record. Business impact: a duplicate record independently frozen until February.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account. 3) Separate flag on the same record: the APEX group is ThoughtSpot, which acquired Mode Analytics. If that group carries larges the account may sit in LE rather than SMB. 4) Raising both together so the grouping is settled before the account is worked. Business impact: either five months of dead hold, or an account worked in the wrong segment.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -887,19 +855,15 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Holdover not reflected/owner change required?</t>
+          <t>Salesforce data issue</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>1) Vir Biotechnology appears twice in the proposed book under one APEX group. 2) Record 001f30000218CZkAAM (Viable, California) arrives August 24, 2026 under Christine McKay. 3) This record is held to Feb 1, 2027 under Eric Witmer. 4) The same company is therefore split across two arrival dates and two current owners because of a duplicate record. Business impact: half of one account is unworkable until February for no reason other than a data duplicate.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
+          <t>Sairam: 1) Vir Biotechnology appears twice in the proposed book under one APEX group. 2) Record 001f30000218CZkAAM (Viable, California) arrives August 24, 2026 under Christine McKay. 3) This record is held to Feb 1, 2027 under Eric Witmer. 4) One company is therefore split across two arrival dates and two current owners purely because of a duplicate record. Business impact: half an account unworkable until February for no reason other than a data duplicate.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -929,36 +893,37 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Holdover not reflected/owner change required?</t>
+          <t>Salesforce data issue</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>1) Enable appears twice in the proposed book under one APEX group. 2) Record 0014y00002rSxEyAAK (Viable, California) is held to Feb 1, 2027 under Abhishek Narayan. 3) This record arrives August 24, 2026 with no current owner recorded. 4) A third record, Enable Benefits (Ontario, Non-Viable), is also held to Feb 1. Business impact: one company split across two arrival dates by duplicate records, with part of it arriving unowned.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+          <t>Sairam: 1) Enable appears twice in the proposed book under one APEX group. 2) Record 0014y00002rSxEyAAK (Viable, California) is held to Feb 1, 2027 under Abhishek Narayan. 3) This record arrives August 24, 2026 with no current owner recorded. 4) A third record, Enable Benefits (Ontario, Non-Viable), is also held to Feb 1. Business impact: one company split across two arrival dates by duplicate records, with part of it arriving unowned.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Before pasting</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Yellow cells need an Opportunity Link pulled from SFDC. Rows marked "None." have no opportunity, which is the evidence itself, so leave that text in place. Category values must be re-picked from the tab drop-down after pasting, since pasted text can break the validation. Paste into your team tab, not this sheet.</t>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Paste into the Ary Tsotras tab, which is shared across his whole team, so the rationales are prefixed with your name to match Wil Pemberton's convention. Category values are the six from the tab's drop-down, so they will validate on paste. Yellow cells need an Opportunity Link from SFDC. Rows reading 'None.' have no opportunity at all, which is the evidence itself, so leave that text in place. Status is left blank, matching the existing rows in the tab.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B13:H13"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Holdover not reflected,Sector classification incorrect,Account size classification incorrect,Buying-center grouping wrong,Salesforce data issue,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/territory/F27-Feedback-Form-Rows.xlsx
+++ b/territory/F27-Feedback-Form-Rows.xlsx
@@ -41,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -85,16 +90,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -468,16 +482,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="108" customWidth="1" min="7" max="7"/>
+    <col width="110" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -526,25 +540,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Federal Home Loan Bank of San Francisco</t>
+          <t>Berje Inc</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/0013300001loDIyAAM/view</t>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001v97U9AAI/view</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Steve Platt</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
           <t>Sairam Gajavelli</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRM: who is it moving to?</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>PASTE OPPORTUNITY LINK</t>
         </is>
@@ -554,373 +568,297 @@
           <t>Holdover not reflected</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) The opportunity on it is dead, with no live communication. 3) A Feb 1 holdover is retained only by moving the opportunity to QO before that date, and a dead cycle has no path there. 4) Named contact Joseph Sacri is known to me from his previous organisation, so there is an existing relationship available to restart it now. Business impact: five months of a restartable relationship going cold before the account changes hands.</t>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Sairam: 1) This account is a DEPARTURE, currently set to move away from me on August 24. 2) There is an FAC on it from my time on the account, run with Jennifer Case. 3) The rules of engagement hold an account with the rep who has an FAC in the last 24 months, moving it February 1 rather than immediately, and that holdover does not appear to have been applied here. 4) Jennifer Case and I intend to work it jointly from here. Business impact: an account with a completed FAC and an active plan behind it reassigned before it has had any chance to reach QO.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Samba Tv, Inc.</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001v8JfRAAU/view</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Josh Scott</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Sairam Gajavelli</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>None. No opportunity exists on this account.</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Holdover not reflected</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account, so nothing can reach QO before the date. 3) ITRG status is Winback, so a lapsed membership sits on the account. 4) Winbacks are the highest-intent accounts in the arriving book and are time-sensitive. Business impact: the strongest re-entry point in the territory sits idle until February.</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Irhythm Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/00140000011lkU3AAI/view</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Cameron McLean</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Sairam Gajavelli</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>None. No opportunity exists on this account.</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Holdover not reflected</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account. 3) Open Opportunities Proposal+ reads 0 in the territory export. 4) With nothing to advance to QO, the holdover has no condition it can satisfy. Business impact: five months of lost coverage on a viable California account with no offsetting continuity benefit.</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/0013300001lNQtMAAW/view</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Akshat Singh</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Sairam Gajavelli</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>None. No opportunity exists on this account.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Holdover not reflected</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account. 3) Separate flag on the same record: the parent/account group is ThoughtSpot, which acquired Mode Analytics. If that group carries larges the account may sit in LE rather than SMB. 4) Raising both together so the grouping is settled before the account is worked. Business impact: either five months of dead hold, or an account worked in the wrong segment.</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Exar Corporation</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>https://infotech.lightning.force.com/lightning/r/Account/0013300001lIyw0AAC/view</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Kevin Gharibizadeh</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Sairam Gajavelli</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>None. No opportunity exists on this account.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Holdover not reflected</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account, so there is nothing to move to QO before Feb 1. 3) Open Opportunities Proposal+ reads 0 in the territory export. 4) Same APEX group as MaxLinear, which is also held and whose opportunity is closed lost, so the group is held as a unit with nothing live in it. Business impact: the holdover cannot achieve its purpose and delays coverage by five months.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Maxlinear</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001whzRcAAI/view</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Kevin Gharibizadeh</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account, so there is nothing to move to QO before Feb 1. 3) Open Opportunities Proposal+ reads 0 in the territory export. 4) Noting that MaxLinear sits in the same parent/account group and is not part of this request, since it carries an opportunity. Business impact: an account with nothing live on it held for five months.</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Black Rock City LLC</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001v97AfAAI/view</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Bell</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Sairam Gajavelli</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>PASTE OPPORTUNITY LINK</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>None. No opportunity exists on this account.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Holdover not reflected</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) The opportunity is closed lost, with no communication on the account. 3) A closed lost opportunity cannot reach QO by Feb 1, so the holdover condition cannot be satisfied. 4) Same APEX group as Exar Corporation, which has no opportunity at all. Business impact: an entire APEX group held for five months with no live cycle in it.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Burning Man Project</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/001a700000LEgFFAA1/view</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Andrew Bell</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover with no opportunity on the record. 2) It is a duplicate of Burning Man Project (001a700000LEgFFAA1), the same organisation in the same parent/account group. Black Rock City LLC is the operating entity behind the event and Burning Man Project is the nonprofit. 3) Burning Man Project carries an opportunity and is not part of this request. 4) The cleanest outcome may be to merge this record into Burning Man Project and let it follow that account. Business impact: a duplicate record held independently until February.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Vir Biotechnology, Inc.</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/001f30000218CZkAAM/view</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Eric Witmer</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Sairam Gajavelli</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>PASTE OPPORTUNITY LINK</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Holdover not reflected</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) The opportunity has died. 3) Black Rock City LLC (001f300001v97AfAAI) is the same organisation in the same APEX group, also held to Feb 1 under the same owner, and is a duplicate record. 4) Asking that both records release together and that Black Rock City LLC merge into this one. Business impact: two records for one organisation both frozen until February on a dead cycle.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Black Rock City LLC</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001v97AfAAI/view</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Andrew Bell</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>None. No opportunity exists on this account.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Salesforce data issue</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Sairam: 1) Vir Biotechnology appears twice in the proposed book under one parent/account group. 2) This record, the Viable California one, is held to Feb 1, 2027 under Eric Witmer. 3) A duplicate, 0014y00003QzArJAAV, is Non-Viable and bills to Colorado, and it arrives August 24, 2026 under Christine McKay. 4) So the workable record is the one being held back, while the redundant one is released early, and the company is split across two dates and two owners by a duplicate. Business impact: the only usable record for this account is frozen until February while its junk duplicate arrives immediately.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Enable</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>https://infotech.lightning.force.com/lightning/r/Account/0014y00002rSxEyAAK/view</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Abhishek Narayan</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Sairam Gajavelli</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>None. No opportunity exists on this account.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Holdover not reflected</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover with no opportunity on the record. 2) Same organisation as Burning Man Project (001a700000LEgFFAA1), same APEX group, same current owner. 3) Black Rock City LLC is the operating entity behind the event and Burning Man Project is the nonprofit. 4) Asking for release alongside Burning Man Project and a merge into that record. Business impact: a duplicate record independently frozen until February.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Samba Tv, Inc.</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/001f300001v8JfRAAU/view</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Josh Scott</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Sairam Gajavelli</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>None. No opportunity exists on this account.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Holdover not reflected</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account, so nothing can reach QO before the date. 3) ITRG status is Winback, so a lapsed membership sits on the account. 4) Winbacks are the highest-intent accounts in the arriving book and are time-sensitive. Business impact: the strongest re-entry point in the territory sits idle until February.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Irhythm Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/00140000011lkU3AAI/view</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Cameron McLean</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Sairam Gajavelli</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>None. No opportunity exists on this account.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Holdover not reflected</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account. 3) Open Opportunities Proposal+ reads 0 in the territory export. 4) With nothing to advance to QO, the holdover has no condition it can satisfy. Business impact: five months of lost coverage on a viable California account with no offsetting continuity benefit.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Mode</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/0013300001lNQtMAAW/view</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Akshat Singh</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Sairam Gajavelli</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>None. No opportunity exists on this account.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Holdover not reflected</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Held to Feb 1, 2027 as an FAC holdover. 2) There is no opportunity on the account. 3) Separate flag on the same record: the APEX group is ThoughtSpot, which acquired Mode Analytics. If that group carries larges the account may sit in LE rather than SMB. 4) Raising both together so the grouping is settled before the account is worked. Business impact: either five months of dead hold, or an account worked in the wrong segment.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Vir Biotechnology, Inc.</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/0014y00003QzArJAAV/view</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Christine McKay</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Sairam Gajavelli</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>None. No opportunity exists on this account.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Salesforce data issue</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Vir Biotechnology appears twice in the proposed book under one APEX group. 2) Record 001f30000218CZkAAM (Viable, California) arrives August 24, 2026 under Christine McKay. 3) This record is held to Feb 1, 2027 under Eric Witmer. 4) One company is therefore split across two arrival dates and two current owners purely because of a duplicate record. Business impact: half an account unworkable until February for no reason other than a data duplicate.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Enable</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>https://infotech.lightning.force.com/lightning/r/Account/001a700000nFDVUAA4/view</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>(none recorded)</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Sairam Gajavelli</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>None. No opportunity exists on this account.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Salesforce data issue</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Sairam: 1) Enable appears twice in the proposed book under one APEX group. 2) Record 0014y00002rSxEyAAK (Viable, California) is held to Feb 1, 2027 under Abhishek Narayan. 3) This record arrives August 24, 2026 with no current owner recorded. 4) A third record, Enable Benefits (Ontario, Non-Viable), is also held to Feb 1. Business impact: one company split across two arrival dates by duplicate records, with part of it arriving unowned.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Sairam: 1) Enable appears three times in the proposed book under one parent/account group. 2) This record, the Viable California one, is held to Feb 1, 2027 under Abhishek Narayan. 3) A duplicate, 001a700000nFDVUAA4, has a blank viability field and arrives August 24, 2026 with no current owner recorded at all. 4) A third record, Enable Benefits (001a7000003nmGQAAY, Ontario, Non-Viable), is also held to Feb 1. Business impact: the usable record is held until February while an unowned duplicate of the same company arrives in August.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Before pasting</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Paste into the Ary Tsotras tab, which is shared across his whole team, so the rationales are prefixed with your name to match Wil Pemberton's convention. Category values are the six from the tab's drop-down, so they will validate on paste. Yellow cells need an Opportunity Link from SFDC. Rows reading 'None.' have no opportunity at all, which is the evidence itself, so leave that text in place. Status is left blank, matching the existing rows in the tab.</t>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Berje Inc (blue row) is the only DEPARTURE here, an account moving away from you. Every other row is an arrival you are asking to receive early. Fill the yellow cells: Berje needs the name of the rep it is moving to, and an Opportunity Link if one exists. Rows reading 'None.' have no opportunity at all, which is the evidence itself, so leave that text in place. Rationales are prefixed with your name because the Ary Tsotras tab is shared across his team. Category values are the six from the tab's drop-down. Status is left blank to match the existing rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B11:H11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Holdover not reflected,Sector classification incorrect,Account size classification incorrect,Buying-center grouping wrong,Salesforce data issue,Other"</formula1>
     </dataValidation>
   </dataValidations>
